--- a/obspy/io/sitexml/tests/data/sera_site_no_analysis.xlsx
+++ b/obspy/io/sitexml/tests/data/sera_site_no_analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiriaki/Desktop/ITSAK/ORFEUS/SITEXML/obspy15/obspy/obspy/io/sitexml/tests/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C006F01F-40F0-4445-9F30-3ED3BE9F7764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{997AB569-5EC2-5746-80B3-E7ED2C26469E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="140">
   <si>
     <t>ownerID</t>
   </si>
@@ -137,9 +137,6 @@
     <t>siteClassEC8_description</t>
   </si>
   <si>
-    <t>siteClassEC8_url</t>
-  </si>
-  <si>
     <t>bedrockDepth_value</t>
   </si>
   <si>
@@ -170,9 +167,6 @@
     <t>bedrockDepth_description</t>
   </si>
   <si>
-    <t>bedrockDepth_url</t>
-  </si>
-  <si>
     <t>h800_value</t>
   </si>
   <si>
@@ -203,9 +197,6 @@
     <t>h800_description</t>
   </si>
   <si>
-    <t>h800_url</t>
-  </si>
-  <si>
     <t>geologicalUnit_value</t>
   </si>
   <si>
@@ -239,9 +230,6 @@
     <t>geologicalUnit_description</t>
   </si>
   <si>
-    <t>geologicalUnit_url</t>
-  </si>
-  <si>
     <t>siteMorphology</t>
   </si>
   <si>
@@ -443,7 +431,16 @@
     <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
   </si>
   <si>
-    <t>quakeml:domain.ab/velocity_profile/006</t>
+    <t>siteClassEC8_uri</t>
+  </si>
+  <si>
+    <t>bedrockDepth_uri</t>
+  </si>
+  <si>
+    <t>h800_uri</t>
+  </si>
+  <si>
+    <t>geologicalUnit_uri</t>
   </si>
 </sst>
 </file>
@@ -1883,61 +1880,61 @@
     </row>
     <row r="2" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="E2" s="15" t="s">
+      <c r="H2" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="L2" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="M2" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="N2" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="G2" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="O2" s="15" t="s">
         <v>124</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="N2" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="O2" s="15" t="s">
-        <v>128</v>
       </c>
       <c r="P2" s="18">
         <v>12345</v>
       </c>
       <c r="Q2" s="15" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="R2" s="15" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S2" s="15" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="T2" s="15" t="s">
         <v>20</v>
@@ -1999,7 +1996,7 @@
         <v>29</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>30</v>
@@ -2026,153 +2023,153 @@
         <v>37</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AH1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="AT1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AS1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="BE1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="BI1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:62" ht="128.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F2" s="4">
         <v>239</v>
@@ -2180,35 +2177,35 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="J2" s="4">
         <v>1</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="M2" s="5"/>
       <c r="N2" s="3">
         <v>2018</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="S2" s="9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="T2" s="4">
         <v>40</v>
@@ -2217,7 +2214,7 @@
         <v>6</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
@@ -2235,11 +2232,11 @@
         <v>1</v>
       </c>
       <c r="AH2" s="9" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AI2" s="5"/>
       <c r="AJ2" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="AK2" s="5"/>
       <c r="AL2" s="3"/>
@@ -2249,72 +2246,72 @@
       <c r="AP2" s="5"/>
       <c r="AQ2" s="5"/>
       <c r="AR2" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AS2" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AT2" s="5"/>
       <c r="AU2" s="5"/>
       <c r="AV2" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AW2" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="AX2" s="5"/>
       <c r="AY2" s="3">
         <v>2018</v>
       </c>
       <c r="AZ2" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="BA2" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="BB2" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="BC2" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="BD2" s="9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="BE2" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="BF2" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="BG2" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="BH2" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="BI2" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="BJ2" s="9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:62" ht="44" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F3" s="7">
         <v>120</v>
@@ -2322,33 +2319,33 @@
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="10" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="J3" s="7">
         <v>1</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M3" s="7"/>
       <c r="N3" s="3">
         <v>2023</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="Q3" s="10" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="R3" s="7"/>
       <c r="S3" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="T3" s="8">
         <v>820</v>
@@ -2358,27 +2355,27 @@
         <v>0.8</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="X3" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="Y3" s="7"/>
       <c r="Z3" s="3">
         <v>2023</v>
       </c>
       <c r="AA3" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="AB3" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="AC3" s="10" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="AD3" s="7"/>
       <c r="AE3" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="AF3" s="8">
         <v>180</v>
@@ -2386,41 +2383,41 @@
       <c r="AG3" s="7"/>
       <c r="AH3" s="7"/>
       <c r="AI3" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="AJ3" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="AK3" s="7"/>
       <c r="AL3" s="3">
         <v>2023</v>
       </c>
       <c r="AM3" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="AN3" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="AO3" s="10" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="AP3" s="7"/>
       <c r="AQ3" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="AR3" s="6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AS3" s="7"/>
       <c r="AT3" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="AU3" s="7"/>
       <c r="AV3" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="AW3" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="AX3" s="7"/>
       <c r="AY3" s="3"/>
@@ -2434,10 +2431,10 @@
       <c r="BG3" s="7"/>
       <c r="BH3" s="7"/>
       <c r="BI3" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="BJ3" s="10" t="s">
-        <v>140</v>
+        <v>112</v>
+      </c>
+      <c r="BJ3" s="6" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/obspy/io/sitexml/tests/data/sera_site_no_analysis.xlsx
+++ b/obspy/io/sitexml/tests/data/sera_site_no_analysis.xlsx
@@ -1,475 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiriaki/Desktop/ITSAK/ORFEUS/SITEXML/obspy15/obspy/obspy/io/sitexml/tests/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{997AB569-5EC2-5746-80B3-E7ED2C26469E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17320" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="siteOwner" sheetId="4" r:id="rId1"/>
-    <sheet name="siteDescription" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="siteOwner" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="siteDescription" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="140">
-  <si>
-    <t>ownerID</t>
-  </si>
-  <si>
-    <t>owner_codename</t>
-  </si>
-  <si>
-    <t>owner_fullname</t>
-  </si>
-  <si>
-    <t>personID</t>
-  </si>
-  <si>
-    <t>person_firstname</t>
-  </si>
-  <si>
-    <t>person_lastname</t>
-  </si>
-  <si>
-    <t>person_mbox</t>
-  </si>
-  <si>
-    <t>person_homepage</t>
-  </si>
-  <si>
-    <t>institutionID</t>
-  </si>
-  <si>
-    <t>institution_name</t>
-  </si>
-  <si>
-    <t>institution_mbox</t>
-  </si>
-  <si>
-    <t>institution_phone</t>
-  </si>
-  <si>
-    <t>institution_homepage</t>
-  </si>
-  <si>
-    <t>address_street</t>
-  </si>
-  <si>
-    <t>address_locality</t>
-  </si>
-  <si>
-    <t>address_postal_code</t>
-  </si>
-  <si>
-    <t>address_country_code</t>
-  </si>
-  <si>
-    <t>address_country</t>
-  </si>
-  <si>
-    <t>affiliation_department</t>
-  </si>
-  <si>
-    <t>affiliation_function</t>
-  </si>
-  <si>
-    <t>Senior researcher</t>
-  </si>
-  <si>
-    <t>siteID</t>
-  </si>
-  <si>
-    <t>siteDescriptionID</t>
-  </si>
-  <si>
-    <t>station</t>
-  </si>
-  <si>
-    <t>latitude</t>
-  </si>
-  <si>
-    <t>longitude</t>
-  </si>
-  <si>
-    <t>altitude</t>
-  </si>
-  <si>
-    <t>minDistanceFromStation</t>
-  </si>
-  <si>
-    <t>maxDistanceFromStation</t>
-  </si>
-  <si>
-    <t>siteClassEC8_value</t>
-  </si>
-  <si>
-    <t>siteClassEC8_title</t>
-  </si>
-  <si>
-    <t>siteClassEC8_firstAuthor</t>
-  </si>
-  <si>
-    <t>siteClassEC8_secondaryAuthors</t>
-  </si>
-  <si>
-    <t>siteClassEC8_year</t>
-  </si>
-  <si>
-    <t>siteClassEC8_booktitle</t>
-  </si>
-  <si>
-    <t>siteClassEC8_language</t>
-  </si>
-  <si>
-    <t>siteClassEC8_doi</t>
-  </si>
-  <si>
-    <t>siteClassEC8_description</t>
-  </si>
-  <si>
-    <t>bedrockDepth_value</t>
-  </si>
-  <si>
-    <t>bedrockDepth_uncertainty</t>
-  </si>
-  <si>
-    <t>bedrockDepth_title</t>
-  </si>
-  <si>
-    <t>bedrockDepth_firstAuthor</t>
-  </si>
-  <si>
-    <t>bedrockDepth_secondaryAuthors</t>
-  </si>
-  <si>
-    <t>bedrockDepth_year</t>
-  </si>
-  <si>
-    <t>bedrockDepth_booktitle</t>
-  </si>
-  <si>
-    <t>bedrockDepth_language</t>
-  </si>
-  <si>
-    <t>bedrockDepth_doi</t>
-  </si>
-  <si>
-    <t>bedrockDepth_description</t>
-  </si>
-  <si>
-    <t>h800_value</t>
-  </si>
-  <si>
-    <t>h800_uncertainty</t>
-  </si>
-  <si>
-    <t>h800_title</t>
-  </si>
-  <si>
-    <t>h800_firstAuthor</t>
-  </si>
-  <si>
-    <t>h800_secondaryAuthors</t>
-  </si>
-  <si>
-    <t>h800_year</t>
-  </si>
-  <si>
-    <t>h800_booktitle</t>
-  </si>
-  <si>
-    <t>h800_language</t>
-  </si>
-  <si>
-    <t>h800_doi</t>
-  </si>
-  <si>
-    <t>h800_description</t>
-  </si>
-  <si>
-    <t>geologicalUnit_value</t>
-  </si>
-  <si>
-    <t>geologicalMapScale</t>
-  </si>
-  <si>
-    <t>geologicalUnitOGE</t>
-  </si>
-  <si>
-    <t>geologicalUnit_title</t>
-  </si>
-  <si>
-    <t>geologicalUnit_firstAuthor</t>
-  </si>
-  <si>
-    <t>geologicalUnit_secondaryAuthors</t>
-  </si>
-  <si>
-    <t>geologicalUnit_year</t>
-  </si>
-  <si>
-    <t>geologicalUnit_booktitle</t>
-  </si>
-  <si>
-    <t>geologicalUnit_language</t>
-  </si>
-  <si>
-    <t>geologicalUnit_doi</t>
-  </si>
-  <si>
-    <t>geologicalUnit_description</t>
-  </si>
-  <si>
-    <t>siteMorphology</t>
-  </si>
-  <si>
-    <t>siteTopography_schemaA</t>
-  </si>
-  <si>
-    <t>siteTopography_schemaB</t>
-  </si>
-  <si>
-    <t>overallQindex</t>
-  </si>
-  <si>
-    <t>preferredSiteAnalysisID</t>
-  </si>
-  <si>
-    <t>preferredVelocityProfileID</t>
-  </si>
-  <si>
-    <t>45.137174</t>
-  </si>
-  <si>
-    <t>5.998905</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
-  </si>
-  <si>
-    <t>Bulletin Earthquake Engineering</t>
-  </si>
-  <si>
-    <t>10.1007/s10518-017-0135-5</t>
-  </si>
-  <si>
-    <t>paper</t>
-  </si>
-  <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>0.43</t>
-  </si>
-  <si>
-    <t>Recent alluvial and lacustrine deposits valley overlying deep Jurassic limestones</t>
-  </si>
-  <si>
-    <t>0.25</t>
-  </si>
-  <si>
-    <t>Slope</t>
-  </si>
-  <si>
-    <t>T1</t>
-  </si>
-  <si>
-    <t>Valley</t>
-  </si>
-  <si>
-    <t>0.41</t>
-  </si>
-  <si>
-    <t>40.555907</t>
-  </si>
-  <si>
-    <t>22.988593</t>
-  </si>
-  <si>
-    <t>10.1002/nsg.12248</t>
-  </si>
-  <si>
-    <t>Holocene Deposits</t>
-  </si>
-  <si>
-    <t>01:50.0</t>
-  </si>
-  <si>
-    <t>IGME map</t>
-  </si>
-  <si>
-    <t>IGME</t>
-  </si>
-  <si>
-    <t>geologicalUnitQindex1</t>
-  </si>
-  <si>
-    <t>siteClassEC8Qindex1</t>
-  </si>
-  <si>
-    <t>bedrockDepthQindex1</t>
-  </si>
-  <si>
-    <t>h800Qindex1</t>
-  </si>
-  <si>
-    <t>en</t>
-  </si>
-  <si>
-    <t>Combination of passive and active methods towards site characterization of accelerometer stations in Greece</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1002/nsg.12248</t>
-  </si>
-  <si>
-    <t>Near Surface Geophysics</t>
-  </si>
-  <si>
-    <t>http://www.domain.ab</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/site/001</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/site_description/001</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/analysis/001</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/velocity_profile/001</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/site/002</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/site_description/002</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/analysis/004</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/siteOwner/001</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/person/001</t>
-  </si>
-  <si>
-    <t>info@domain.ab</t>
-  </si>
-  <si>
-    <t>https://www.domain.ab/person</t>
-  </si>
-  <si>
-    <t>someemail@domain.ab</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Surname</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/institution/001</t>
-  </si>
-  <si>
-    <t>INSTITUTION_ABBR</t>
-  </si>
-  <si>
-    <t>+30 123 456789</t>
-  </si>
-  <si>
-    <t>Some streetAddress</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>AB</t>
-  </si>
-  <si>
-    <t>Somecountry</t>
-  </si>
-  <si>
-    <t>Seismology</t>
-  </si>
-  <si>
-    <t>SITEOWNER</t>
-  </si>
-  <si>
-    <t>Site Owner Full Name</t>
-  </si>
-  <si>
-    <t>ABCD</t>
-  </si>
-  <si>
-    <t>ZWXY</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Author A.</t>
-  </si>
-  <si>
-    <t>Author B.</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
-  </si>
-  <si>
-    <t>siteClassEC8_uri</t>
-  </si>
-  <si>
-    <t>bedrockDepth_uri</t>
-  </si>
-  <si>
-    <t>h800_uri</t>
-  </si>
-  <si>
-    <t>geologicalUnit_uri</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <name val="Helvetica Neue"/>
+      <color indexed="8"/>
       <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color indexed="8"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
+      <b val="1"/>
+      <color indexed="8"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color indexed="8"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
+      <color indexed="8"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -560,81 +130,81 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="21">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{600E5E3E-3C3F-3D42-957F-EDF86D356745}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -703,14 +273,6 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1785,663 +1347,1003 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C7AE111-1EFA-E748-84E0-0CB676D8C6E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" style="13" customWidth="1"/>
-    <col min="3" max="3" width="17.5" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.5" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" style="13" customWidth="1"/>
-    <col min="6" max="6" width="15.1640625" style="13" customWidth="1"/>
-    <col min="7" max="7" width="34.1640625" style="13" customWidth="1"/>
-    <col min="8" max="8" width="54.83203125" style="13" customWidth="1"/>
-    <col min="9" max="9" width="29" style="13" customWidth="1"/>
-    <col min="10" max="10" width="17" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" style="13" customWidth="1"/>
-    <col min="12" max="12" width="15.1640625" style="13" customWidth="1"/>
-    <col min="13" max="13" width="18.6640625" style="13" customWidth="1"/>
-    <col min="14" max="14" width="28.6640625" style="13" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" style="13" customWidth="1"/>
-    <col min="16" max="16" width="18.33203125" style="13" customWidth="1"/>
-    <col min="17" max="17" width="19.5" style="13" customWidth="1"/>
-    <col min="18" max="18" width="14.6640625" style="13" customWidth="1"/>
-    <col min="19" max="19" width="18.83203125" style="13" customWidth="1"/>
-    <col min="20" max="20" width="16.1640625" style="13" customWidth="1"/>
-    <col min="21" max="21" width="8.33203125" style="13" customWidth="1"/>
-    <col min="22" max="16384" width="8.33203125" style="13"/>
+    <col width="30.33203125" bestFit="1" customWidth="1" style="13" min="1" max="1"/>
+    <col width="15.6640625" customWidth="1" style="13" min="2" max="2"/>
+    <col width="17.5" bestFit="1" customWidth="1" style="13" min="3" max="3"/>
+    <col width="25.5" bestFit="1" customWidth="1" style="13" min="4" max="4"/>
+    <col width="15.33203125" customWidth="1" style="13" min="5" max="5"/>
+    <col width="15.1640625" customWidth="1" style="13" min="6" max="6"/>
+    <col width="34.1640625" customWidth="1" style="13" min="7" max="7"/>
+    <col width="54.83203125" customWidth="1" style="13" min="8" max="8"/>
+    <col width="29" customWidth="1" style="13" min="9" max="9"/>
+    <col width="17" bestFit="1" customWidth="1" style="13" min="10" max="10"/>
+    <col width="14.6640625" customWidth="1" style="13" min="11" max="11"/>
+    <col width="15.1640625" customWidth="1" style="13" min="12" max="12"/>
+    <col width="18.6640625" customWidth="1" style="13" min="13" max="13"/>
+    <col width="28.6640625" customWidth="1" style="13" min="14" max="14"/>
+    <col width="14.33203125" customWidth="1" style="13" min="15" max="15"/>
+    <col width="18.33203125" customWidth="1" style="13" min="16" max="16"/>
+    <col width="19.5" customWidth="1" style="13" min="17" max="17"/>
+    <col width="14.6640625" customWidth="1" style="13" min="18" max="18"/>
+    <col width="18.83203125" customWidth="1" style="13" min="19" max="19"/>
+    <col width="16.1640625" customWidth="1" style="13" min="20" max="20"/>
+    <col width="8.33203125" customWidth="1" style="13" min="21" max="21"/>
+    <col width="8.33203125" customWidth="1" style="13" min="22" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="12" t="s">
-        <v>19</v>
+    <row r="1" ht="20.25" customHeight="1" s="20">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>ownerID</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>owner_codename</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>owner_fullname</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>personID</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>person_firstname</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>person_lastname</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>person_mbox</t>
+        </is>
+      </c>
+      <c r="H1" s="12" t="inlineStr">
+        <is>
+          <t>person_homepage</t>
+        </is>
+      </c>
+      <c r="I1" s="12" t="inlineStr">
+        <is>
+          <t>institutionID</t>
+        </is>
+      </c>
+      <c r="J1" s="12" t="inlineStr">
+        <is>
+          <t>institution_name</t>
+        </is>
+      </c>
+      <c r="K1" s="12" t="inlineStr">
+        <is>
+          <t>institution_mbox</t>
+        </is>
+      </c>
+      <c r="L1" s="12" t="inlineStr">
+        <is>
+          <t>institution_phone</t>
+        </is>
+      </c>
+      <c r="M1" s="12" t="inlineStr">
+        <is>
+          <t>institution_homepage</t>
+        </is>
+      </c>
+      <c r="N1" s="12" t="inlineStr">
+        <is>
+          <t>address_street</t>
+        </is>
+      </c>
+      <c r="O1" s="12" t="inlineStr">
+        <is>
+          <t>address_locality</t>
+        </is>
+      </c>
+      <c r="P1" s="12" t="inlineStr">
+        <is>
+          <t>address_postal_code</t>
+        </is>
+      </c>
+      <c r="Q1" s="12" t="inlineStr">
+        <is>
+          <t>address_country_code</t>
+        </is>
+      </c>
+      <c r="R1" s="12" t="inlineStr">
+        <is>
+          <t>address_country</t>
+        </is>
+      </c>
+      <c r="S1" s="12" t="inlineStr">
+        <is>
+          <t>affiliation_department</t>
+        </is>
+      </c>
+      <c r="T1" s="12" t="inlineStr">
+        <is>
+          <t>affiliation_function</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="N2" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="O2" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="P2" s="18">
+    <row r="2" ht="20.25" customHeight="1" s="20">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/siteOwner/001</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>SITEOWNER</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>Site Owner Full Name</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/person/001</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>Surname</t>
+        </is>
+      </c>
+      <c r="G2" s="16" t="inlineStr">
+        <is>
+          <t>someemail@domain.ab</t>
+        </is>
+      </c>
+      <c r="H2" s="15" t="inlineStr">
+        <is>
+          <t>https://www.domain.ab/person</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/institution/001</t>
+        </is>
+      </c>
+      <c r="J2" s="15" t="inlineStr">
+        <is>
+          <t>INSTITUTION_ABBR</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>info@domain.ab</t>
+        </is>
+      </c>
+      <c r="L2" s="17" t="inlineStr">
+        <is>
+          <t>+30 123 456789</t>
+        </is>
+      </c>
+      <c r="M2" s="15" t="inlineStr">
+        <is>
+          <t>http://www.domain.ab</t>
+        </is>
+      </c>
+      <c r="N2" s="15" t="inlineStr">
+        <is>
+          <t>Some streetAddress</t>
+        </is>
+      </c>
+      <c r="O2" s="15" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="P2" s="18" t="n">
         <v>12345</v>
       </c>
-      <c r="Q2" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="R2" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="S2" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="T2" s="15" t="s">
-        <v>20</v>
+      <c r="Q2" s="15" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="R2" s="15" t="inlineStr">
+        <is>
+          <t>Somecountry</t>
+        </is>
+      </c>
+      <c r="S2" s="15" t="inlineStr">
+        <is>
+          <t>Seismology</t>
+        </is>
+      </c>
+      <c r="T2" s="15" t="inlineStr">
+        <is>
+          <t>Senior researcher</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="isterre.fr/person/001" xr:uid="{B524591F-5FF0-224F-AE21-10B1AFE4E766}"/>
-    <hyperlink ref="M2" r:id="rId2" display="http://www.isterre.fr" xr:uid="{A4CF2504-4AF0-074F-AEE2-E6DBA31220CC}"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" display="isterre.fr/person/001" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" display="http://www.isterre.fr" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
   <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BJ3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="9" width="16.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="19.6640625" style="2" customWidth="1"/>
-    <col min="11" max="63" width="16.33203125" style="2" customWidth="1"/>
-    <col min="64" max="16384" width="16.33203125" style="2"/>
+    <col width="16.33203125" customWidth="1" style="2" min="1" max="9"/>
+    <col width="19.6640625" customWidth="1" style="2" min="10" max="10"/>
+    <col width="16.33203125" customWidth="1" style="2" min="11" max="63"/>
+    <col width="16.33203125" customWidth="1" style="2" min="64" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="W1" s="1" t="s">
+    <row r="1" ht="32.25" customHeight="1" s="20">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>siteID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>siteDescriptionID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>station</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>altitude</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>minDistanceFromStation</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>maxDistanceFromStation</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8Qindex1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8_title</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8_firstAuthor</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8_secondaryAuthors</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8_year</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8_booktitle</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8_language</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8_doi</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8_description</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8_uri</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_value</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_uncertainty</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepthQindex1</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_title</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_firstAuthor</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_secondaryAuthors</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_year</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_booktitle</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_language</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_doi</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_description</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_uri</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>h800_value</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>h800_uncertainty</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>h800Qindex1</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>h800_title</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>h800_firstAuthor</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>h800_secondaryAuthors</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>h800_year</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>h800_booktitle</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>h800_language</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>h800_doi</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>h800_description</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>h800_uri</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnit_value</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnitQindex1</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalMapScale</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnitOGE</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnit_title</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnit_firstAuthor</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnit_secondaryAuthors</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnit_year</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnit_booktitle</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnit_language</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnit_doi</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnit_description</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnit_uri</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>siteMorphology</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>siteTopography_schemaA</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>siteTopography_schemaB</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>overallQindex</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>preferredSiteAnalysisID</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>preferredVelocityProfileID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="128.25" customHeight="1" s="20">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site/001</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site_description/001</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>45.137174</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>5.998905</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>239</v>
+      </c>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
+        </is>
+      </c>
+      <c r="L2" s="9" t="inlineStr">
+        <is>
+          <t>Author A.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="3" t="n">
+        <v>2018</v>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>Bulletin Earthquake Engineering</t>
+        </is>
+      </c>
+      <c r="P2" s="9" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>10.1007/s10518-017-0135-5</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="S2" s="9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="X1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="BF1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="BI1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>74</v>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="n"/>
+      <c r="X2" s="5" t="n"/>
+      <c r="Y2" s="5" t="n"/>
+      <c r="Z2" s="3" t="n"/>
+      <c r="AA2" s="5" t="n"/>
+      <c r="AB2" s="5" t="n"/>
+      <c r="AC2" s="5" t="n"/>
+      <c r="AD2" s="5" t="n"/>
+      <c r="AE2" s="5" t="n"/>
+      <c r="AF2" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="9" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="AI2" s="5" t="inlineStr">
+        <is>
+          <t>Some title</t>
+        </is>
+      </c>
+      <c r="AJ2" s="9" t="inlineStr">
+        <is>
+          <t>Author A.</t>
+        </is>
+      </c>
+      <c r="AK2" s="5" t="n"/>
+      <c r="AL2" s="3" t="n"/>
+      <c r="AM2" s="5" t="n"/>
+      <c r="AN2" s="5" t="n"/>
+      <c r="AO2" s="5" t="n"/>
+      <c r="AP2" s="5" t="n"/>
+      <c r="AQ2" s="5" t="n"/>
+      <c r="AR2" s="3" t="inlineStr">
+        <is>
+          <t>Recent alluvial and lacustrine deposits valley overlying deep Jurassic limestones</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AT2" s="5" t="n"/>
+      <c r="AU2" s="5" t="n"/>
+      <c r="AV2" s="3" t="inlineStr">
+        <is>
+          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
+        </is>
+      </c>
+      <c r="AW2" s="9" t="inlineStr">
+        <is>
+          <t>Author A.</t>
+        </is>
+      </c>
+      <c r="AX2" s="5" t="n"/>
+      <c r="AY2" s="3" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AZ2" s="3" t="inlineStr">
+        <is>
+          <t>Bulletin Earthquake Engineering</t>
+        </is>
+      </c>
+      <c r="BA2" s="9" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="BB2" s="3" t="inlineStr">
+        <is>
+          <t>10.1007/s10518-017-0135-5</t>
+        </is>
+      </c>
+      <c r="BC2" s="3" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="BD2" s="9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
+        </is>
+      </c>
+      <c r="BE2" s="3" t="inlineStr">
+        <is>
+          <t>Slope</t>
+        </is>
+      </c>
+      <c r="BF2" s="3" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="BG2" s="3" t="inlineStr">
+        <is>
+          <t>Valley</t>
+        </is>
+      </c>
+      <c r="BH2" s="3" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="BI2" s="3" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/analysis/001</t>
+        </is>
+      </c>
+      <c r="BJ2" s="9" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/velocity_profile/001</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:62" ht="128.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F2" s="4">
-        <v>239</v>
-      </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="J2" s="4">
+    <row r="3" ht="44" customHeight="1" s="20">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site/002</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site_description/002</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>ZWXY</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>40.555907</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>22.988593</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="M2" s="5"/>
-      <c r="N2" s="3">
-        <v>2018</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="P2" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="S2" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="T2" s="4">
-        <v>40</v>
-      </c>
-      <c r="U2" s="4">
-        <v>6</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
-      <c r="AF2" s="4">
-        <v>10</v>
-      </c>
-      <c r="AG2" s="4">
-        <v>1</v>
-      </c>
-      <c r="AH2" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AI2" s="5"/>
-      <c r="AJ2" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="AK2" s="5"/>
-      <c r="AL2" s="3"/>
-      <c r="AM2" s="5"/>
-      <c r="AN2" s="5"/>
-      <c r="AO2" s="5"/>
-      <c r="AP2" s="5"/>
-      <c r="AQ2" s="5"/>
-      <c r="AR2" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AS2" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AT2" s="5"/>
-      <c r="AU2" s="5"/>
-      <c r="AV2" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AW2" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="AX2" s="5"/>
-      <c r="AY2" s="3">
-        <v>2018</v>
-      </c>
-      <c r="AZ2" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="BA2" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="BB2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="BC2" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="BD2" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="BF2" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="BG2" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="BH2" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="BI2" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="BJ2" s="9" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:62" ht="44" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" s="7">
-        <v>120</v>
-      </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="J3" s="7">
-        <v>1</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="M3" s="7"/>
-      <c r="N3" s="3">
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Combination of passive and active methods towards site characterization of accelerometer stations in Greece</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Author B.</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="n"/>
+      <c r="N3" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="O3" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="P3" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q3" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="R3" s="7"/>
-      <c r="S3" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="T3" s="8">
+      <c r="O3" s="11" t="inlineStr">
+        <is>
+          <t>Near Surface Geophysics</t>
+        </is>
+      </c>
+      <c r="P3" s="11" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="Q3" s="10" t="inlineStr">
+        <is>
+          <t>10.1002/nsg.12248</t>
+        </is>
+      </c>
+      <c r="R3" s="8" t="n"/>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/nsg.12248</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
         <v>820</v>
       </c>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7">
+      <c r="U3" s="8" t="n"/>
+      <c r="V3" s="8" t="n">
         <v>0.8</v>
       </c>
-      <c r="W3" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="X3" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="3">
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>Combination of passive and active methods towards site characterization of accelerometer stations in Greece</t>
+        </is>
+      </c>
+      <c r="X3" s="10" t="inlineStr">
+        <is>
+          <t>Author B.</t>
+        </is>
+      </c>
+      <c r="Y3" s="8" t="n"/>
+      <c r="Z3" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="AA3" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB3" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="AC3" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD3" s="7"/>
-      <c r="AE3" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AF3" s="8">
+      <c r="AA3" s="11" t="inlineStr">
+        <is>
+          <t>Near Surface Geophysics</t>
+        </is>
+      </c>
+      <c r="AB3" s="11" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AC3" s="10" t="inlineStr">
+        <is>
+          <t>10.1002/nsg.12248</t>
+        </is>
+      </c>
+      <c r="AD3" s="8" t="n"/>
+      <c r="AE3" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/nsg.12248</t>
+        </is>
+      </c>
+      <c r="AF3" s="8" t="n">
         <v>180</v>
       </c>
-      <c r="AG3" s="7"/>
-      <c r="AH3" s="7"/>
-      <c r="AI3" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="AJ3" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK3" s="7"/>
-      <c r="AL3" s="3">
+      <c r="AG3" s="8" t="n"/>
+      <c r="AH3" s="8" t="n"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>Combination of passive and active methods towards site characterization of accelerometer stations in Greece</t>
+        </is>
+      </c>
+      <c r="AJ3" s="10" t="inlineStr">
+        <is>
+          <t>Author B.</t>
+        </is>
+      </c>
+      <c r="AK3" s="8" t="n"/>
+      <c r="AL3" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="AM3" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="AN3" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="AO3" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="AP3" s="7"/>
-      <c r="AQ3" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AR3" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="AS3" s="7"/>
-      <c r="AT3" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU3" s="7"/>
-      <c r="AV3" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="AW3" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="AX3" s="7"/>
-      <c r="AY3" s="3"/>
-      <c r="AZ3" s="7"/>
-      <c r="BA3" s="7"/>
-      <c r="BB3" s="7"/>
-      <c r="BC3" s="7"/>
-      <c r="BD3" s="7"/>
-      <c r="BE3" s="7"/>
-      <c r="BF3" s="7"/>
-      <c r="BG3" s="7"/>
-      <c r="BH3" s="7"/>
-      <c r="BI3" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="BJ3" s="6" t="s">
-        <v>112</v>
+      <c r="AM3" s="11" t="inlineStr">
+        <is>
+          <t>Near Surface Geophysics</t>
+        </is>
+      </c>
+      <c r="AN3" s="11" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AO3" s="10" t="inlineStr">
+        <is>
+          <t>10.1002/nsg.12248</t>
+        </is>
+      </c>
+      <c r="AP3" s="8" t="n"/>
+      <c r="AQ3" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/nsg.12248</t>
+        </is>
+      </c>
+      <c r="AR3" s="6" t="inlineStr">
+        <is>
+          <t>Holocene Deposits</t>
+        </is>
+      </c>
+      <c r="AS3" s="8" t="n"/>
+      <c r="AT3" s="6" t="inlineStr">
+        <is>
+          <t>01:50.0</t>
+        </is>
+      </c>
+      <c r="AU3" s="8" t="n"/>
+      <c r="AV3" s="6" t="inlineStr">
+        <is>
+          <t>IGME map</t>
+        </is>
+      </c>
+      <c r="AW3" s="6" t="inlineStr">
+        <is>
+          <t>IGME</t>
+        </is>
+      </c>
+      <c r="AX3" s="8" t="n"/>
+      <c r="AY3" s="3" t="n"/>
+      <c r="AZ3" s="8" t="n"/>
+      <c r="BA3" s="8" t="n"/>
+      <c r="BB3" s="8" t="n"/>
+      <c r="BC3" s="8" t="n"/>
+      <c r="BD3" s="8" t="n"/>
+      <c r="BE3" s="8" t="n"/>
+      <c r="BF3" s="8" t="n"/>
+      <c r="BG3" s="8" t="n"/>
+      <c r="BH3" s="8" t="n"/>
+      <c r="BI3" s="6" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/analysis/004</t>
+        </is>
+      </c>
+      <c r="BJ3" s="6" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/analysis/004</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
   <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>
--- a/obspy/io/sitexml/tests/data/sera_site_no_analysis.xlsx
+++ b/obspy/io/sitexml/tests/data/sera_site_no_analysis.xlsx
@@ -1939,7 +1939,7 @@
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>ABCD</t>
+          <t>XX.ABCD</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>ZWXY</t>
+          <t>YY.ZWXY</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">

--- a/obspy/io/sitexml/tests/data/sera_site_no_analysis.xlsx
+++ b/obspy/io/sitexml/tests/data/sera_site_no_analysis.xlsx
@@ -1,45 +1,478 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiriaki/Desktop/ITSAK/ORFEUS/SITEXML/obspy15/obspy/obspy/io/sitexml/tests/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD36B93-0C7D-7F48-88A9-4659F9E44048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17320" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="siteOwner" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="siteDescription" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="siteOwner" sheetId="1" r:id="rId1"/>
+    <sheet name="siteDescription" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="141">
+  <si>
+    <t>siteID</t>
+  </si>
+  <si>
+    <t>siteDescriptionID</t>
+  </si>
+  <si>
+    <t>station</t>
+  </si>
+  <si>
+    <t>latitude</t>
+  </si>
+  <si>
+    <t>longitude</t>
+  </si>
+  <si>
+    <t>altitude</t>
+  </si>
+  <si>
+    <t>minDistanceFromStation</t>
+  </si>
+  <si>
+    <t>maxDistanceFromStation</t>
+  </si>
+  <si>
+    <t>siteClassEC8_value</t>
+  </si>
+  <si>
+    <t>siteClassEC8Qindex1</t>
+  </si>
+  <si>
+    <t>siteClassEC8_title</t>
+  </si>
+  <si>
+    <t>siteClassEC8_firstAuthor</t>
+  </si>
+  <si>
+    <t>siteClassEC8_secondaryAuthors</t>
+  </si>
+  <si>
+    <t>siteClassEC8_year</t>
+  </si>
+  <si>
+    <t>siteClassEC8_booktitle</t>
+  </si>
+  <si>
+    <t>siteClassEC8_language</t>
+  </si>
+  <si>
+    <t>siteClassEC8_doi</t>
+  </si>
+  <si>
+    <t>siteClassEC8_description</t>
+  </si>
+  <si>
+    <t>siteClassEC8_uri</t>
+  </si>
+  <si>
+    <t>bedrockDepth_value</t>
+  </si>
+  <si>
+    <t>bedrockDepth_uncertainty</t>
+  </si>
+  <si>
+    <t>bedrockDepthQindex1</t>
+  </si>
+  <si>
+    <t>bedrockDepth_title</t>
+  </si>
+  <si>
+    <t>bedrockDepth_firstAuthor</t>
+  </si>
+  <si>
+    <t>bedrockDepth_secondaryAuthors</t>
+  </si>
+  <si>
+    <t>bedrockDepth_year</t>
+  </si>
+  <si>
+    <t>bedrockDepth_booktitle</t>
+  </si>
+  <si>
+    <t>bedrockDepth_language</t>
+  </si>
+  <si>
+    <t>bedrockDepth_doi</t>
+  </si>
+  <si>
+    <t>bedrockDepth_description</t>
+  </si>
+  <si>
+    <t>bedrockDepth_uri</t>
+  </si>
+  <si>
+    <t>h800_value</t>
+  </si>
+  <si>
+    <t>h800_uncertainty</t>
+  </si>
+  <si>
+    <t>h800Qindex1</t>
+  </si>
+  <si>
+    <t>h800_title</t>
+  </si>
+  <si>
+    <t>h800_firstAuthor</t>
+  </si>
+  <si>
+    <t>h800_secondaryAuthors</t>
+  </si>
+  <si>
+    <t>h800_year</t>
+  </si>
+  <si>
+    <t>h800_booktitle</t>
+  </si>
+  <si>
+    <t>h800_language</t>
+  </si>
+  <si>
+    <t>h800_doi</t>
+  </si>
+  <si>
+    <t>h800_description</t>
+  </si>
+  <si>
+    <t>h800_uri</t>
+  </si>
+  <si>
+    <t>geologicalUnit_value</t>
+  </si>
+  <si>
+    <t>geologicalUnitQindex1</t>
+  </si>
+  <si>
+    <t>geologicalMapScale</t>
+  </si>
+  <si>
+    <t>geologicalUnitOGE</t>
+  </si>
+  <si>
+    <t>geologicalUnit_title</t>
+  </si>
+  <si>
+    <t>geologicalUnit_firstAuthor</t>
+  </si>
+  <si>
+    <t>geologicalUnit_secondaryAuthors</t>
+  </si>
+  <si>
+    <t>geologicalUnit_year</t>
+  </si>
+  <si>
+    <t>geologicalUnit_booktitle</t>
+  </si>
+  <si>
+    <t>geologicalUnit_language</t>
+  </si>
+  <si>
+    <t>geologicalUnit_doi</t>
+  </si>
+  <si>
+    <t>geologicalUnit_description</t>
+  </si>
+  <si>
+    <t>geologicalUnit_uri</t>
+  </si>
+  <si>
+    <t>siteMorphology</t>
+  </si>
+  <si>
+    <t>siteTopography_schemaA</t>
+  </si>
+  <si>
+    <t>siteTopography_schemaB</t>
+  </si>
+  <si>
+    <t>overallQindex</t>
+  </si>
+  <si>
+    <t>preferredSiteAnalysisID</t>
+  </si>
+  <si>
+    <t>preferredVelocityProfileID</t>
+  </si>
+  <si>
+    <t>quakeml:domain.ab/site/001</t>
+  </si>
+  <si>
+    <t>quakeml:domain.ab/site_description/001</t>
+  </si>
+  <si>
+    <t>XX.ABCD</t>
+  </si>
+  <si>
+    <t>45.137174</t>
+  </si>
+  <si>
+    <t>5.998905</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
+  </si>
+  <si>
+    <t>Author A.</t>
+  </si>
+  <si>
+    <t>Bulletin Earthquake Engineering</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>10.1007/s10518-017-0135-5</t>
+  </si>
+  <si>
+    <t>paper</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t>Some title</t>
+  </si>
+  <si>
+    <t>Recent alluvial and lacustrine deposits valley overlying deep Jurassic limestones</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>Valley</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>quakeml:domain.ab/analysis/001</t>
+  </si>
+  <si>
+    <t>quakeml:domain.ab/velocity_profile/001</t>
+  </si>
+  <si>
+    <t>quakeml:domain.ab/site/002</t>
+  </si>
+  <si>
+    <t>quakeml:domain.ab/site_description/002</t>
+  </si>
+  <si>
+    <t>YY.ZWXY</t>
+  </si>
+  <si>
+    <t>40.555907</t>
+  </si>
+  <si>
+    <t>22.988593</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Combination of passive and active methods towards site characterization of accelerometer stations in Greece</t>
+  </si>
+  <si>
+    <t>Author B.</t>
+  </si>
+  <si>
+    <t>Near Surface Geophysics</t>
+  </si>
+  <si>
+    <t>10.1002/nsg.12248</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1002/nsg.12248</t>
+  </si>
+  <si>
+    <t>Holocene Deposits</t>
+  </si>
+  <si>
+    <t>01:50.0</t>
+  </si>
+  <si>
+    <t>IGME map</t>
+  </si>
+  <si>
+    <t>IGME</t>
+  </si>
+  <si>
+    <t>quakeml:domain.ab/analysis/004</t>
+  </si>
+  <si>
+    <t>ownerID</t>
+  </si>
+  <si>
+    <t>owner_codename</t>
+  </si>
+  <si>
+    <t>owner_fullname</t>
+  </si>
+  <si>
+    <t>personID</t>
+  </si>
+  <si>
+    <t>person_firstname</t>
+  </si>
+  <si>
+    <t>person_lastname</t>
+  </si>
+  <si>
+    <t>person_mbox</t>
+  </si>
+  <si>
+    <t>person_homepage</t>
+  </si>
+  <si>
+    <t>institutionID</t>
+  </si>
+  <si>
+    <t>institution_name</t>
+  </si>
+  <si>
+    <t>institution_mbox</t>
+  </si>
+  <si>
+    <t>institution_phone</t>
+  </si>
+  <si>
+    <t>institution_homepage</t>
+  </si>
+  <si>
+    <t>address_street</t>
+  </si>
+  <si>
+    <t>address_locality</t>
+  </si>
+  <si>
+    <t>address_postal_code</t>
+  </si>
+  <si>
+    <t>address_country_code</t>
+  </si>
+  <si>
+    <t>address_country</t>
+  </si>
+  <si>
+    <t>affiliation_department</t>
+  </si>
+  <si>
+    <t>affiliation_function</t>
+  </si>
+  <si>
+    <t>quakeml:domain.ab/siteOwner/001</t>
+  </si>
+  <si>
+    <t>SITEOWNER</t>
+  </si>
+  <si>
+    <t>Site Owner Full Name</t>
+  </si>
+  <si>
+    <t>quakeml:domain.ab/person/001</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Surname</t>
+  </si>
+  <si>
+    <t>someemail@domain.ab</t>
+  </si>
+  <si>
+    <t>https://www.domain.ab/person</t>
+  </si>
+  <si>
+    <t>quakeml:domain.ab/institution/001</t>
+  </si>
+  <si>
+    <t>INSTITUTION_ABBR</t>
+  </si>
+  <si>
+    <t>info@domain.ab</t>
+  </si>
+  <si>
+    <t>+30 123 456789</t>
+  </si>
+  <si>
+    <t>http://www.domain.ab</t>
+  </si>
+  <si>
+    <t>Some streetAddress</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>Somecountry</t>
+  </si>
+  <si>
+    <t>Seismology</t>
+  </si>
+  <si>
+    <t>Senior researcher</t>
+  </si>
+  <si>
+    <t>Valley - Basin</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="10"/>
+      <color indexed="8"/>
       <name val="Helvetica Neue"/>
-      <color indexed="8"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="8"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
-      <b val="1"/>
-      <color indexed="8"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color indexed="8"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
-      <color indexed="8"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -130,80 +563,71 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -273,6 +697,14 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1347,1003 +1779,664 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col width="30.33203125" bestFit="1" customWidth="1" style="13" min="1" max="1"/>
-    <col width="15.6640625" customWidth="1" style="13" min="2" max="2"/>
-    <col width="17.5" bestFit="1" customWidth="1" style="13" min="3" max="3"/>
-    <col width="25.5" bestFit="1" customWidth="1" style="13" min="4" max="4"/>
-    <col width="15.33203125" customWidth="1" style="13" min="5" max="5"/>
-    <col width="15.1640625" customWidth="1" style="13" min="6" max="6"/>
-    <col width="34.1640625" customWidth="1" style="13" min="7" max="7"/>
-    <col width="54.83203125" customWidth="1" style="13" min="8" max="8"/>
-    <col width="29" customWidth="1" style="13" min="9" max="9"/>
-    <col width="17" bestFit="1" customWidth="1" style="13" min="10" max="10"/>
-    <col width="14.6640625" customWidth="1" style="13" min="11" max="11"/>
-    <col width="15.1640625" customWidth="1" style="13" min="12" max="12"/>
-    <col width="18.6640625" customWidth="1" style="13" min="13" max="13"/>
-    <col width="28.6640625" customWidth="1" style="13" min="14" max="14"/>
-    <col width="14.33203125" customWidth="1" style="13" min="15" max="15"/>
-    <col width="18.33203125" customWidth="1" style="13" min="16" max="16"/>
-    <col width="19.5" customWidth="1" style="13" min="17" max="17"/>
-    <col width="14.6640625" customWidth="1" style="13" min="18" max="18"/>
-    <col width="18.83203125" customWidth="1" style="13" min="19" max="19"/>
-    <col width="16.1640625" customWidth="1" style="13" min="20" max="20"/>
-    <col width="8.33203125" customWidth="1" style="13" min="21" max="21"/>
-    <col width="8.33203125" customWidth="1" style="13" min="22" max="16384"/>
+    <col min="1" max="1" width="30.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="17.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="15.1640625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="34.1640625" style="10" customWidth="1"/>
+    <col min="8" max="8" width="54.83203125" style="10" customWidth="1"/>
+    <col min="9" max="9" width="29" style="10" customWidth="1"/>
+    <col min="10" max="10" width="17" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" style="10" customWidth="1"/>
+    <col min="12" max="12" width="15.1640625" style="10" customWidth="1"/>
+    <col min="13" max="13" width="18.6640625" style="10" customWidth="1"/>
+    <col min="14" max="14" width="28.6640625" style="10" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" style="10" customWidth="1"/>
+    <col min="16" max="16" width="18.33203125" style="10" customWidth="1"/>
+    <col min="17" max="17" width="19.5" style="10" customWidth="1"/>
+    <col min="18" max="18" width="14.6640625" style="10" customWidth="1"/>
+    <col min="19" max="19" width="18.83203125" style="10" customWidth="1"/>
+    <col min="20" max="20" width="16.1640625" style="10" customWidth="1"/>
+    <col min="21" max="22" width="8.33203125" style="10" customWidth="1"/>
+    <col min="23" max="16384" width="8.33203125" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1" s="20">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>ownerID</t>
-        </is>
-      </c>
-      <c r="B1" s="12" t="inlineStr">
-        <is>
-          <t>owner_codename</t>
-        </is>
-      </c>
-      <c r="C1" s="12" t="inlineStr">
-        <is>
-          <t>owner_fullname</t>
-        </is>
-      </c>
-      <c r="D1" s="12" t="inlineStr">
-        <is>
-          <t>personID</t>
-        </is>
-      </c>
-      <c r="E1" s="12" t="inlineStr">
-        <is>
-          <t>person_firstname</t>
-        </is>
-      </c>
-      <c r="F1" s="12" t="inlineStr">
-        <is>
-          <t>person_lastname</t>
-        </is>
-      </c>
-      <c r="G1" s="12" t="inlineStr">
-        <is>
-          <t>person_mbox</t>
-        </is>
-      </c>
-      <c r="H1" s="12" t="inlineStr">
-        <is>
-          <t>person_homepage</t>
-        </is>
-      </c>
-      <c r="I1" s="12" t="inlineStr">
-        <is>
-          <t>institutionID</t>
-        </is>
-      </c>
-      <c r="J1" s="12" t="inlineStr">
-        <is>
-          <t>institution_name</t>
-        </is>
-      </c>
-      <c r="K1" s="12" t="inlineStr">
-        <is>
-          <t>institution_mbox</t>
-        </is>
-      </c>
-      <c r="L1" s="12" t="inlineStr">
-        <is>
-          <t>institution_phone</t>
-        </is>
-      </c>
-      <c r="M1" s="12" t="inlineStr">
-        <is>
-          <t>institution_homepage</t>
-        </is>
-      </c>
-      <c r="N1" s="12" t="inlineStr">
-        <is>
-          <t>address_street</t>
-        </is>
-      </c>
-      <c r="O1" s="12" t="inlineStr">
-        <is>
-          <t>address_locality</t>
-        </is>
-      </c>
-      <c r="P1" s="12" t="inlineStr">
-        <is>
-          <t>address_postal_code</t>
-        </is>
-      </c>
-      <c r="Q1" s="12" t="inlineStr">
-        <is>
-          <t>address_country_code</t>
-        </is>
-      </c>
-      <c r="R1" s="12" t="inlineStr">
-        <is>
-          <t>address_country</t>
-        </is>
-      </c>
-      <c r="S1" s="12" t="inlineStr">
-        <is>
-          <t>affiliation_department</t>
-        </is>
-      </c>
-      <c r="T1" s="12" t="inlineStr">
-        <is>
-          <t>affiliation_function</t>
-        </is>
+    <row r="1" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="S1" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="T1" s="9" t="s">
+        <v>120</v>
       </c>
     </row>
-    <row r="2" ht="20.25" customHeight="1" s="20">
-      <c r="A2" s="19" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/siteOwner/001</t>
-        </is>
-      </c>
-      <c r="B2" s="14" t="inlineStr">
-        <is>
-          <t>SITEOWNER</t>
-        </is>
-      </c>
-      <c r="C2" s="15" t="inlineStr">
-        <is>
-          <t>Site Owner Full Name</t>
-        </is>
-      </c>
-      <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/person/001</t>
-        </is>
-      </c>
-      <c r="E2" s="15" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="F2" s="15" t="inlineStr">
-        <is>
-          <t>Surname</t>
-        </is>
-      </c>
-      <c r="G2" s="16" t="inlineStr">
-        <is>
-          <t>someemail@domain.ab</t>
-        </is>
-      </c>
-      <c r="H2" s="15" t="inlineStr">
-        <is>
-          <t>https://www.domain.ab/person</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/institution/001</t>
-        </is>
-      </c>
-      <c r="J2" s="15" t="inlineStr">
-        <is>
-          <t>INSTITUTION_ABBR</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>info@domain.ab</t>
-        </is>
-      </c>
-      <c r="L2" s="17" t="inlineStr">
-        <is>
-          <t>+30 123 456789</t>
-        </is>
-      </c>
-      <c r="M2" s="15" t="inlineStr">
-        <is>
-          <t>http://www.domain.ab</t>
-        </is>
-      </c>
-      <c r="N2" s="15" t="inlineStr">
-        <is>
-          <t>Some streetAddress</t>
-        </is>
-      </c>
-      <c r="O2" s="15" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="P2" s="18" t="n">
+    <row r="2" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="P2" s="15">
         <v>12345</v>
       </c>
-      <c r="Q2" s="15" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="R2" s="15" t="inlineStr">
-        <is>
-          <t>Somecountry</t>
-        </is>
-      </c>
-      <c r="S2" s="15" t="inlineStr">
-        <is>
-          <t>Seismology</t>
-        </is>
-      </c>
-      <c r="T2" s="15" t="inlineStr">
-        <is>
-          <t>Senior researcher</t>
-        </is>
+      <c r="Q2" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="T2" s="12" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" display="isterre.fr/person/001" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" display="http://www.isterre.fr" r:id="rId2"/>
+    <hyperlink ref="D2" r:id="rId1" display="isterre.fr/person/001" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="M2" r:id="rId2" display="http://www.isterre.fr" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
   <headerFooter>
-    <oddHeader/>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BJ3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col width="16.33203125" customWidth="1" style="2" min="1" max="9"/>
-    <col width="19.6640625" customWidth="1" style="2" min="10" max="10"/>
-    <col width="16.33203125" customWidth="1" style="2" min="11" max="63"/>
-    <col width="16.33203125" customWidth="1" style="2" min="64" max="16384"/>
+    <col min="1" max="9" width="16.33203125" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" customWidth="1"/>
+    <col min="11" max="64" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32.25" customHeight="1" s="20">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>siteID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>siteDescriptionID</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>latitude</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>longitude</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>altitude</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>minDistanceFromStation</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>maxDistanceFromStation</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>siteClassEC8_value</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>siteClassEC8Qindex1</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>siteClassEC8_title</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>siteClassEC8_firstAuthor</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>siteClassEC8_secondaryAuthors</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>siteClassEC8_year</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>siteClassEC8_booktitle</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>siteClassEC8_language</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>siteClassEC8_doi</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>siteClassEC8_description</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>siteClassEC8_uri</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>bedrockDepth_value</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>bedrockDepth_uncertainty</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>bedrockDepthQindex1</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>bedrockDepth_title</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>bedrockDepth_firstAuthor</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>bedrockDepth_secondaryAuthors</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>bedrockDepth_year</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>bedrockDepth_booktitle</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>bedrockDepth_language</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>bedrockDepth_doi</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>bedrockDepth_description</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>bedrockDepth_uri</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>h800_value</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>h800_uncertainty</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>h800Qindex1</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>h800_title</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>h800_firstAuthor</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>h800_secondaryAuthors</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>h800_year</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>h800_booktitle</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>h800_language</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>h800_doi</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>h800_description</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>h800_uri</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>geologicalUnit_value</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>geologicalUnitQindex1</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>geologicalMapScale</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>geologicalUnitOGE</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>geologicalUnit_title</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>geologicalUnit_firstAuthor</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>geologicalUnit_secondaryAuthors</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>geologicalUnit_year</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>geologicalUnit_booktitle</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>geologicalUnit_language</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>geologicalUnit_doi</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>geologicalUnit_description</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>geologicalUnit_uri</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>siteMorphology</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>siteTopography_schemaA</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>siteTopography_schemaB</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>overallQindex</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>preferredSiteAnalysisID</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>preferredVelocityProfileID</t>
-        </is>
+    <row r="1" spans="1:62" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="2" ht="128.25" customHeight="1" s="20">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/site/001</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/site_description/001</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>XX.ABCD</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>45.137174</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>5.998905</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="n">
+    <row r="2" spans="1:62" ht="128.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="3">
         <v>239</v>
       </c>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="n">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="3">
         <v>1</v>
       </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
-        </is>
-      </c>
-      <c r="L2" s="9" t="inlineStr">
-        <is>
-          <t>Author A.</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="3" t="n">
+      <c r="K2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M2" s="3"/>
+      <c r="N2" s="2">
         <v>2018</v>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>Bulletin Earthquake Engineering</t>
-        </is>
-      </c>
-      <c r="P2" s="9" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>10.1007/s10518-017-0135-5</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>paper</t>
-        </is>
-      </c>
-      <c r="S2" s="9" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
-        </is>
-      </c>
-      <c r="T2" s="5" t="n">
+      <c r="O2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="T2" s="3">
         <v>40</v>
       </c>
-      <c r="U2" s="5" t="n">
+      <c r="U2" s="3">
         <v>6</v>
       </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="W2" s="5" t="n"/>
-      <c r="X2" s="5" t="n"/>
-      <c r="Y2" s="5" t="n"/>
-      <c r="Z2" s="3" t="n"/>
-      <c r="AA2" s="5" t="n"/>
-      <c r="AB2" s="5" t="n"/>
-      <c r="AC2" s="5" t="n"/>
-      <c r="AD2" s="5" t="n"/>
-      <c r="AE2" s="5" t="n"/>
-      <c r="AF2" s="5" t="n">
+      <c r="V2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3">
         <v>10</v>
       </c>
-      <c r="AG2" s="5" t="n">
+      <c r="AG2" s="3">
         <v>1</v>
       </c>
-      <c r="AH2" s="9" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
-      </c>
-      <c r="AI2" s="5" t="inlineStr">
-        <is>
-          <t>Some title</t>
-        </is>
-      </c>
-      <c r="AJ2" s="9" t="inlineStr">
-        <is>
-          <t>Author A.</t>
-        </is>
-      </c>
-      <c r="AK2" s="5" t="n"/>
-      <c r="AL2" s="3" t="n"/>
-      <c r="AM2" s="5" t="n"/>
-      <c r="AN2" s="5" t="n"/>
-      <c r="AO2" s="5" t="n"/>
-      <c r="AP2" s="5" t="n"/>
-      <c r="AQ2" s="5" t="n"/>
-      <c r="AR2" s="3" t="inlineStr">
-        <is>
-          <t>Recent alluvial and lacustrine deposits valley overlying deep Jurassic limestones</t>
-        </is>
-      </c>
-      <c r="AS2" s="3" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="AT2" s="5" t="n"/>
-      <c r="AU2" s="5" t="n"/>
-      <c r="AV2" s="3" t="inlineStr">
-        <is>
-          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
-        </is>
-      </c>
-      <c r="AW2" s="9" t="inlineStr">
-        <is>
-          <t>Author A.</t>
-        </is>
-      </c>
-      <c r="AX2" s="5" t="n"/>
-      <c r="AY2" s="3" t="n">
+      <c r="AH2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ2" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK2" s="3"/>
+      <c r="AL2" s="2"/>
+      <c r="AM2" s="3"/>
+      <c r="AN2" s="3"/>
+      <c r="AO2" s="3"/>
+      <c r="AP2" s="3"/>
+      <c r="AQ2" s="3"/>
+      <c r="AR2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AT2" s="3"/>
+      <c r="AU2" s="3"/>
+      <c r="AV2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AW2" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AX2" s="3"/>
+      <c r="AY2" s="2">
         <v>2018</v>
       </c>
-      <c r="AZ2" s="3" t="inlineStr">
-        <is>
-          <t>Bulletin Earthquake Engineering</t>
-        </is>
-      </c>
-      <c r="BA2" s="9" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="BB2" s="3" t="inlineStr">
-        <is>
-          <t>10.1007/s10518-017-0135-5</t>
-        </is>
-      </c>
-      <c r="BC2" s="3" t="inlineStr">
-        <is>
-          <t>paper</t>
-        </is>
-      </c>
-      <c r="BD2" s="9" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
-        </is>
-      </c>
-      <c r="BE2" s="3" t="inlineStr">
-        <is>
-          <t>Slope</t>
-        </is>
-      </c>
-      <c r="BF2" s="3" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="BG2" s="3" t="inlineStr">
-        <is>
-          <t>Valley</t>
-        </is>
-      </c>
-      <c r="BH2" s="3" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="BI2" s="3" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/analysis/001</t>
-        </is>
-      </c>
-      <c r="BJ2" s="9" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/velocity_profile/001</t>
-        </is>
+      <c r="AZ2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="BA2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="BB2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="BC2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="BD2" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE2" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BF2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BG2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="BH2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="BI2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="BJ2" s="6" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="3" ht="44" customHeight="1" s="20">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/site/002</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/site_description/002</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>YY.ZWXY</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>40.555907</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>22.988593</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="n">
+    <row r="3" spans="1:62" ht="44" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" s="5">
         <v>120</v>
       </c>
-      <c r="G3" s="8" t="n"/>
-      <c r="H3" s="8" t="n"/>
-      <c r="I3" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="n">
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="J3" s="5">
         <v>1</v>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Combination of passive and active methods towards site characterization of accelerometer stations in Greece</t>
-        </is>
-      </c>
-      <c r="L3" s="10" t="inlineStr">
-        <is>
-          <t>Author B.</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="n"/>
-      <c r="N3" s="3" t="n">
+      <c r="K3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="M3" s="5"/>
+      <c r="N3" s="2">
         <v>2023</v>
       </c>
-      <c r="O3" s="11" t="inlineStr">
-        <is>
-          <t>Near Surface Geophysics</t>
-        </is>
-      </c>
-      <c r="P3" s="11" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="Q3" s="10" t="inlineStr">
-        <is>
-          <t>10.1002/nsg.12248</t>
-        </is>
-      </c>
-      <c r="R3" s="8" t="n"/>
-      <c r="S3" s="6" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/nsg.12248</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
+      <c r="O3" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="R3" s="5"/>
+      <c r="S3" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="T3" s="5">
         <v>820</v>
       </c>
-      <c r="U3" s="8" t="n"/>
-      <c r="V3" s="8" t="n">
+      <c r="U3" s="5"/>
+      <c r="V3" s="5">
         <v>0.8</v>
       </c>
-      <c r="W3" s="3" t="inlineStr">
-        <is>
-          <t>Combination of passive and active methods towards site characterization of accelerometer stations in Greece</t>
-        </is>
-      </c>
-      <c r="X3" s="10" t="inlineStr">
-        <is>
-          <t>Author B.</t>
-        </is>
-      </c>
-      <c r="Y3" s="8" t="n"/>
-      <c r="Z3" s="3" t="n">
+      <c r="W3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="X3" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="2">
         <v>2023</v>
       </c>
-      <c r="AA3" s="11" t="inlineStr">
-        <is>
-          <t>Near Surface Geophysics</t>
-        </is>
-      </c>
-      <c r="AB3" s="11" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="AC3" s="10" t="inlineStr">
-        <is>
-          <t>10.1002/nsg.12248</t>
-        </is>
-      </c>
-      <c r="AD3" s="8" t="n"/>
-      <c r="AE3" s="6" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/nsg.12248</t>
-        </is>
-      </c>
-      <c r="AF3" s="8" t="n">
+      <c r="AA3" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC3" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD3" s="5"/>
+      <c r="AE3" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF3" s="5">
         <v>180</v>
       </c>
-      <c r="AG3" s="8" t="n"/>
-      <c r="AH3" s="8" t="n"/>
-      <c r="AI3" s="3" t="inlineStr">
-        <is>
-          <t>Combination of passive and active methods towards site characterization of accelerometer stations in Greece</t>
-        </is>
-      </c>
-      <c r="AJ3" s="10" t="inlineStr">
-        <is>
-          <t>Author B.</t>
-        </is>
-      </c>
-      <c r="AK3" s="8" t="n"/>
-      <c r="AL3" s="3" t="n">
+      <c r="AG3" s="5"/>
+      <c r="AH3" s="5"/>
+      <c r="AI3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AJ3" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK3" s="5"/>
+      <c r="AL3" s="2">
         <v>2023</v>
       </c>
-      <c r="AM3" s="11" t="inlineStr">
-        <is>
-          <t>Near Surface Geophysics</t>
-        </is>
-      </c>
-      <c r="AN3" s="11" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="AO3" s="10" t="inlineStr">
-        <is>
-          <t>10.1002/nsg.12248</t>
-        </is>
-      </c>
-      <c r="AP3" s="8" t="n"/>
-      <c r="AQ3" s="6" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/nsg.12248</t>
-        </is>
-      </c>
-      <c r="AR3" s="6" t="inlineStr">
-        <is>
-          <t>Holocene Deposits</t>
-        </is>
-      </c>
-      <c r="AS3" s="8" t="n"/>
-      <c r="AT3" s="6" t="inlineStr">
-        <is>
-          <t>01:50.0</t>
-        </is>
-      </c>
-      <c r="AU3" s="8" t="n"/>
-      <c r="AV3" s="6" t="inlineStr">
-        <is>
-          <t>IGME map</t>
-        </is>
-      </c>
-      <c r="AW3" s="6" t="inlineStr">
-        <is>
-          <t>IGME</t>
-        </is>
-      </c>
-      <c r="AX3" s="8" t="n"/>
-      <c r="AY3" s="3" t="n"/>
-      <c r="AZ3" s="8" t="n"/>
-      <c r="BA3" s="8" t="n"/>
-      <c r="BB3" s="8" t="n"/>
-      <c r="BC3" s="8" t="n"/>
-      <c r="BD3" s="8" t="n"/>
-      <c r="BE3" s="8" t="n"/>
-      <c r="BF3" s="8" t="n"/>
-      <c r="BG3" s="8" t="n"/>
-      <c r="BH3" s="8" t="n"/>
-      <c r="BI3" s="6" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/analysis/004</t>
-        </is>
-      </c>
-      <c r="BJ3" s="6" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/analysis/004</t>
-        </is>
+      <c r="AM3" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AO3" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="AP3" s="5"/>
+      <c r="AQ3" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="AR3" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS3" s="5"/>
+      <c r="AT3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="AU3" s="5"/>
+      <c r="AV3" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW3" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="AX3" s="5"/>
+      <c r="AY3" s="2"/>
+      <c r="AZ3" s="5"/>
+      <c r="BA3" s="5"/>
+      <c r="BB3" s="5"/>
+      <c r="BC3" s="5"/>
+      <c r="BD3" s="5"/>
+      <c r="BE3" s="5"/>
+      <c r="BF3" s="5"/>
+      <c r="BG3" s="5"/>
+      <c r="BH3" s="5"/>
+      <c r="BI3" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="BJ3" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
   <headerFooter>
-    <oddHeader/>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>
--- a/obspy/io/sitexml/tests/data/sera_site_no_analysis.xlsx
+++ b/obspy/io/sitexml/tests/data/sera_site_no_analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiriaki/Desktop/ITSAK/ORFEUS/SITEXML/obspy15/obspy/obspy/io/sitexml/tests/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD36B93-0C7D-7F48-88A9-4659F9E44048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84630149-4DBC-9542-B3DD-77F3CE195730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="136">
   <si>
     <t>siteID</t>
   </si>
@@ -203,12 +203,6 @@
     <t>overallQindex</t>
   </si>
   <si>
-    <t>preferredSiteAnalysisID</t>
-  </si>
-  <si>
-    <t>preferredVelocityProfileID</t>
-  </si>
-  <si>
     <t>quakeml:domain.ab/site/001</t>
   </si>
   <si>
@@ -272,12 +266,6 @@
     <t>0.41</t>
   </si>
   <si>
-    <t>quakeml:domain.ab/analysis/001</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/velocity_profile/001</t>
-  </si>
-  <si>
     <t>quakeml:domain.ab/site/002</t>
   </si>
   <si>
@@ -321,9 +309,6 @@
   </si>
   <si>
     <t>IGME</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/analysis/004</t>
   </si>
   <si>
     <t>ownerID</t>
@@ -1812,126 +1797,126 @@
   <sheetData>
     <row r="1" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="N1" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="R1" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="S1" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="T1" s="9" t="s">
         <v>115</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="R1" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="S1" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="T1" s="9" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="G2" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="H2" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="I2" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="J2" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="K2" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="L2" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="M2" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="N2" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="O2" s="12" t="s">
         <v>130</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="L2" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="N2" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>135</v>
       </c>
       <c r="P2" s="15">
         <v>12345</v>
       </c>
       <c r="Q2" s="12" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="R2" s="12" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="S2" s="12" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="T2" s="12" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1952,15 +1937,15 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BJ3"/>
+  <dimension ref="A1:BH3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="9" width="16.33203125" customWidth="1"/>
     <col min="10" max="10" width="19.6640625" customWidth="1"/>
-    <col min="11" max="64" width="16.33203125" customWidth="1"/>
+    <col min="11" max="62" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:60" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2141,28 +2126,22 @@
       <c r="BH1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:60" ht="128.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="2" spans="1:62" ht="128.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="2" t="s">
+      <c r="C2" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="E2" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="F2" s="3">
         <v>239</v>
@@ -2170,35 +2149,35 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J2" s="3">
         <v>1</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="2">
         <v>2018</v>
       </c>
       <c r="O2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="R2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="S2" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="T2" s="3">
         <v>40</v>
@@ -2207,7 +2186,7 @@
         <v>6</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
@@ -2225,13 +2204,13 @@
         <v>1</v>
       </c>
       <c r="AH2" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AI2" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AJ2" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AK2" s="3"/>
       <c r="AL2" s="2"/>
@@ -2241,72 +2220,66 @@
       <c r="AP2" s="3"/>
       <c r="AQ2" s="3"/>
       <c r="AR2" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AT2" s="3"/>
       <c r="AU2" s="3"/>
       <c r="AV2" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AW2" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AX2" s="3"/>
       <c r="AY2" s="2">
         <v>2018</v>
       </c>
       <c r="AZ2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="BA2" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="BB2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="BA2" s="6" t="s">
+      <c r="BC2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="BB2" s="2" t="s">
+      <c r="BD2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="BC2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="BD2" s="6" t="s">
-        <v>74</v>
-      </c>
       <c r="BE2" s="6" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="BF2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="BG2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="BG2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:60" ht="44" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="BH2" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="BI2" s="2" t="s">
+      <c r="C3" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="BJ2" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="3" spans="1:62" ht="44" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="F3" s="5">
         <v>120</v>
@@ -2314,33 +2287,33 @@
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="J3" s="5">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M3" s="5"/>
       <c r="N3" s="2">
         <v>2023</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="R3" s="5"/>
       <c r="S3" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="T3" s="5">
         <v>820</v>
@@ -2350,27 +2323,27 @@
         <v>0.8</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="X3" s="7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Y3" s="5"/>
       <c r="Z3" s="2">
         <v>2023</v>
       </c>
       <c r="AA3" s="8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AB3" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AC3" s="7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="AD3" s="5"/>
       <c r="AE3" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="AF3" s="5">
         <v>180</v>
@@ -2378,41 +2351,41 @@
       <c r="AG3" s="5"/>
       <c r="AH3" s="5"/>
       <c r="AI3" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AJ3" s="7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="AK3" s="5"/>
       <c r="AL3" s="2">
         <v>2023</v>
       </c>
       <c r="AM3" s="8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AN3" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AO3" s="7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="AP3" s="5"/>
       <c r="AQ3" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="AR3" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="AS3" s="5"/>
       <c r="AT3" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AU3" s="5"/>
       <c r="AV3" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="AW3" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="AX3" s="5"/>
       <c r="AY3" s="2"/>
@@ -2425,12 +2398,6 @@
       <c r="BF3" s="5"/>
       <c r="BG3" s="5"/>
       <c r="BH3" s="5"/>
-      <c r="BI3" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="BJ3" s="4" t="s">
-        <v>100</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>

--- a/obspy/io/sitexml/tests/data/sera_site_no_analysis.xlsx
+++ b/obspy/io/sitexml/tests/data/sera_site_no_analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiriaki/Desktop/ITSAK/ORFEUS/SITEXML/obspy15/obspy/obspy/io/sitexml/tests/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84630149-4DBC-9542-B3DD-77F3CE195730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1260012-5A11-0F44-897C-49CAE454C09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -272,9 +272,6 @@
     <t>quakeml:domain.ab/site_description/002</t>
   </si>
   <si>
-    <t>YY.ZWXY</t>
-  </si>
-  <si>
     <t>40.555907</t>
   </si>
   <si>
@@ -429,6 +426,9 @@
   </si>
   <si>
     <t>Valley - Basin</t>
+  </si>
+  <si>
+    <t>YY.WXYZ</t>
   </si>
 </sst>
 </file>
@@ -1797,126 +1797,126 @@
   <sheetData>
     <row r="1" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="R1" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="S1" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="T1" s="9" t="s">
         <v>114</v>
-      </c>
-      <c r="T1" s="9" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="I2" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="K2" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="M2" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="N2" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="O2" s="12" t="s">
         <v>129</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>130</v>
       </c>
       <c r="P2" s="15">
         <v>12345</v>
       </c>
       <c r="Q2" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="R2" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="S2" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="S2" s="12" t="s">
+      <c r="T2" s="12" t="s">
         <v>133</v>
-      </c>
-      <c r="T2" s="12" t="s">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2253,7 +2253,7 @@
         <v>72</v>
       </c>
       <c r="BE2" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="BF2" s="2" t="s">
         <v>78</v>
@@ -2273,13 +2273,13 @@
         <v>82</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>85</v>
       </c>
       <c r="F3" s="5">
         <v>120</v>
@@ -2287,33 +2287,33 @@
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J3" s="5">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L3" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>88</v>
       </c>
       <c r="M3" s="5"/>
       <c r="N3" s="2">
         <v>2023</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P3" s="8" t="s">
         <v>69</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R3" s="5"/>
       <c r="S3" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T3" s="5">
         <v>820</v>
@@ -2323,27 +2323,27 @@
         <v>0.8</v>
       </c>
       <c r="W3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="X3" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="X3" s="7" t="s">
-        <v>88</v>
       </c>
       <c r="Y3" s="5"/>
       <c r="Z3" s="2">
         <v>2023</v>
       </c>
       <c r="AA3" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AB3" s="8" t="s">
         <v>69</v>
       </c>
       <c r="AC3" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AD3" s="5"/>
       <c r="AE3" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AF3" s="5">
         <v>180</v>
@@ -2351,41 +2351,41 @@
       <c r="AG3" s="5"/>
       <c r="AH3" s="5"/>
       <c r="AI3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AJ3" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="AJ3" s="7" t="s">
-        <v>88</v>
       </c>
       <c r="AK3" s="5"/>
       <c r="AL3" s="2">
         <v>2023</v>
       </c>
       <c r="AM3" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AN3" s="8" t="s">
         <v>69</v>
       </c>
       <c r="AO3" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AP3" s="5"/>
       <c r="AQ3" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AR3" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="AR3" s="4" t="s">
-        <v>92</v>
       </c>
       <c r="AS3" s="5"/>
       <c r="AT3" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AU3" s="5"/>
       <c r="AV3" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW3" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="AW3" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="AX3" s="5"/>
       <c r="AY3" s="2"/>

--- a/obspy/io/sitexml/tests/data/sera_site_no_analysis.xlsx
+++ b/obspy/io/sitexml/tests/data/sera_site_no_analysis.xlsx
@@ -1,463 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiriaki/Desktop/ITSAK/ORFEUS/SITEXML/obspy15/obspy/obspy/io/sitexml/tests/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1260012-5A11-0F44-897C-49CAE454C09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17320" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="siteOwner" sheetId="1" r:id="rId1"/>
-    <sheet name="siteDescription" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="siteOwner" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="siteDescription" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="136">
-  <si>
-    <t>siteID</t>
-  </si>
-  <si>
-    <t>siteDescriptionID</t>
-  </si>
-  <si>
-    <t>station</t>
-  </si>
-  <si>
-    <t>latitude</t>
-  </si>
-  <si>
-    <t>longitude</t>
-  </si>
-  <si>
-    <t>altitude</t>
-  </si>
-  <si>
-    <t>minDistanceFromStation</t>
-  </si>
-  <si>
-    <t>maxDistanceFromStation</t>
-  </si>
-  <si>
-    <t>siteClassEC8_value</t>
-  </si>
-  <si>
-    <t>siteClassEC8Qindex1</t>
-  </si>
-  <si>
-    <t>siteClassEC8_title</t>
-  </si>
-  <si>
-    <t>siteClassEC8_firstAuthor</t>
-  </si>
-  <si>
-    <t>siteClassEC8_secondaryAuthors</t>
-  </si>
-  <si>
-    <t>siteClassEC8_year</t>
-  </si>
-  <si>
-    <t>siteClassEC8_booktitle</t>
-  </si>
-  <si>
-    <t>siteClassEC8_language</t>
-  </si>
-  <si>
-    <t>siteClassEC8_doi</t>
-  </si>
-  <si>
-    <t>siteClassEC8_description</t>
-  </si>
-  <si>
-    <t>siteClassEC8_uri</t>
-  </si>
-  <si>
-    <t>bedrockDepth_value</t>
-  </si>
-  <si>
-    <t>bedrockDepth_uncertainty</t>
-  </si>
-  <si>
-    <t>bedrockDepthQindex1</t>
-  </si>
-  <si>
-    <t>bedrockDepth_title</t>
-  </si>
-  <si>
-    <t>bedrockDepth_firstAuthor</t>
-  </si>
-  <si>
-    <t>bedrockDepth_secondaryAuthors</t>
-  </si>
-  <si>
-    <t>bedrockDepth_year</t>
-  </si>
-  <si>
-    <t>bedrockDepth_booktitle</t>
-  </si>
-  <si>
-    <t>bedrockDepth_language</t>
-  </si>
-  <si>
-    <t>bedrockDepth_doi</t>
-  </si>
-  <si>
-    <t>bedrockDepth_description</t>
-  </si>
-  <si>
-    <t>bedrockDepth_uri</t>
-  </si>
-  <si>
-    <t>h800_value</t>
-  </si>
-  <si>
-    <t>h800_uncertainty</t>
-  </si>
-  <si>
-    <t>h800Qindex1</t>
-  </si>
-  <si>
-    <t>h800_title</t>
-  </si>
-  <si>
-    <t>h800_firstAuthor</t>
-  </si>
-  <si>
-    <t>h800_secondaryAuthors</t>
-  </si>
-  <si>
-    <t>h800_year</t>
-  </si>
-  <si>
-    <t>h800_booktitle</t>
-  </si>
-  <si>
-    <t>h800_language</t>
-  </si>
-  <si>
-    <t>h800_doi</t>
-  </si>
-  <si>
-    <t>h800_description</t>
-  </si>
-  <si>
-    <t>h800_uri</t>
-  </si>
-  <si>
-    <t>geologicalUnit_value</t>
-  </si>
-  <si>
-    <t>geologicalUnitQindex1</t>
-  </si>
-  <si>
-    <t>geologicalMapScale</t>
-  </si>
-  <si>
-    <t>geologicalUnitOGE</t>
-  </si>
-  <si>
-    <t>geologicalUnit_title</t>
-  </si>
-  <si>
-    <t>geologicalUnit_firstAuthor</t>
-  </si>
-  <si>
-    <t>geologicalUnit_secondaryAuthors</t>
-  </si>
-  <si>
-    <t>geologicalUnit_year</t>
-  </si>
-  <si>
-    <t>geologicalUnit_booktitle</t>
-  </si>
-  <si>
-    <t>geologicalUnit_language</t>
-  </si>
-  <si>
-    <t>geologicalUnit_doi</t>
-  </si>
-  <si>
-    <t>geologicalUnit_description</t>
-  </si>
-  <si>
-    <t>geologicalUnit_uri</t>
-  </si>
-  <si>
-    <t>siteMorphology</t>
-  </si>
-  <si>
-    <t>siteTopography_schemaA</t>
-  </si>
-  <si>
-    <t>siteTopography_schemaB</t>
-  </si>
-  <si>
-    <t>overallQindex</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/site/001</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/site_description/001</t>
-  </si>
-  <si>
-    <t>XX.ABCD</t>
-  </si>
-  <si>
-    <t>45.137174</t>
-  </si>
-  <si>
-    <t>5.998905</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
-  </si>
-  <si>
-    <t>Author A.</t>
-  </si>
-  <si>
-    <t>Bulletin Earthquake Engineering</t>
-  </si>
-  <si>
-    <t>en</t>
-  </si>
-  <si>
-    <t>10.1007/s10518-017-0135-5</t>
-  </si>
-  <si>
-    <t>paper</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
-  </si>
-  <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>0.43</t>
-  </si>
-  <si>
-    <t>Some title</t>
-  </si>
-  <si>
-    <t>Recent alluvial and lacustrine deposits valley overlying deep Jurassic limestones</t>
-  </si>
-  <si>
-    <t>0.25</t>
-  </si>
-  <si>
-    <t>T1</t>
-  </si>
-  <si>
-    <t>Valley</t>
-  </si>
-  <si>
-    <t>0.41</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/site/002</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/site_description/002</t>
-  </si>
-  <si>
-    <t>40.555907</t>
-  </si>
-  <si>
-    <t>22.988593</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Combination of passive and active methods towards site characterization of accelerometer stations in Greece</t>
-  </si>
-  <si>
-    <t>Author B.</t>
-  </si>
-  <si>
-    <t>Near Surface Geophysics</t>
-  </si>
-  <si>
-    <t>10.1002/nsg.12248</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1002/nsg.12248</t>
-  </si>
-  <si>
-    <t>Holocene Deposits</t>
-  </si>
-  <si>
-    <t>01:50.0</t>
-  </si>
-  <si>
-    <t>IGME map</t>
-  </si>
-  <si>
-    <t>IGME</t>
-  </si>
-  <si>
-    <t>ownerID</t>
-  </si>
-  <si>
-    <t>owner_codename</t>
-  </si>
-  <si>
-    <t>owner_fullname</t>
-  </si>
-  <si>
-    <t>personID</t>
-  </si>
-  <si>
-    <t>person_firstname</t>
-  </si>
-  <si>
-    <t>person_lastname</t>
-  </si>
-  <si>
-    <t>person_mbox</t>
-  </si>
-  <si>
-    <t>person_homepage</t>
-  </si>
-  <si>
-    <t>institutionID</t>
-  </si>
-  <si>
-    <t>institution_name</t>
-  </si>
-  <si>
-    <t>institution_mbox</t>
-  </si>
-  <si>
-    <t>institution_phone</t>
-  </si>
-  <si>
-    <t>institution_homepage</t>
-  </si>
-  <si>
-    <t>address_street</t>
-  </si>
-  <si>
-    <t>address_locality</t>
-  </si>
-  <si>
-    <t>address_postal_code</t>
-  </si>
-  <si>
-    <t>address_country_code</t>
-  </si>
-  <si>
-    <t>address_country</t>
-  </si>
-  <si>
-    <t>affiliation_department</t>
-  </si>
-  <si>
-    <t>affiliation_function</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/siteOwner/001</t>
-  </si>
-  <si>
-    <t>SITEOWNER</t>
-  </si>
-  <si>
-    <t>Site Owner Full Name</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/person/001</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Surname</t>
-  </si>
-  <si>
-    <t>someemail@domain.ab</t>
-  </si>
-  <si>
-    <t>https://www.domain.ab/person</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/institution/001</t>
-  </si>
-  <si>
-    <t>INSTITUTION_ABBR</t>
-  </si>
-  <si>
-    <t>info@domain.ab</t>
-  </si>
-  <si>
-    <t>+30 123 456789</t>
-  </si>
-  <si>
-    <t>http://www.domain.ab</t>
-  </si>
-  <si>
-    <t>Some streetAddress</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>AB</t>
-  </si>
-  <si>
-    <t>Somecountry</t>
-  </si>
-  <si>
-    <t>Seismology</t>
-  </si>
-  <si>
-    <t>Senior researcher</t>
-  </si>
-  <si>
-    <t>Valley - Basin</t>
-  </si>
-  <si>
-    <t>YY.WXYZ</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <name val="Helvetica Neue"/>
+      <color indexed="8"/>
       <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color indexed="8"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
+      <b val="1"/>
+      <color indexed="8"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color indexed="8"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
+      <color indexed="8"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -548,71 +130,71 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -682,14 +264,6 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1764,646 +1338,972 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="17.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" style="10" customWidth="1"/>
-    <col min="6" max="6" width="15.1640625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="34.1640625" style="10" customWidth="1"/>
-    <col min="8" max="8" width="54.83203125" style="10" customWidth="1"/>
-    <col min="9" max="9" width="29" style="10" customWidth="1"/>
-    <col min="10" max="10" width="17" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" style="10" customWidth="1"/>
-    <col min="12" max="12" width="15.1640625" style="10" customWidth="1"/>
-    <col min="13" max="13" width="18.6640625" style="10" customWidth="1"/>
-    <col min="14" max="14" width="28.6640625" style="10" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" style="10" customWidth="1"/>
-    <col min="16" max="16" width="18.33203125" style="10" customWidth="1"/>
-    <col min="17" max="17" width="19.5" style="10" customWidth="1"/>
-    <col min="18" max="18" width="14.6640625" style="10" customWidth="1"/>
-    <col min="19" max="19" width="18.83203125" style="10" customWidth="1"/>
-    <col min="20" max="20" width="16.1640625" style="10" customWidth="1"/>
-    <col min="21" max="22" width="8.33203125" style="10" customWidth="1"/>
-    <col min="23" max="16384" width="8.33203125" style="10"/>
+    <col width="30.33203125" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
+    <col width="15.6640625" customWidth="1" style="10" min="2" max="2"/>
+    <col width="17.5" bestFit="1" customWidth="1" style="10" min="3" max="3"/>
+    <col width="25.5" bestFit="1" customWidth="1" style="10" min="4" max="4"/>
+    <col width="15.33203125" customWidth="1" style="10" min="5" max="5"/>
+    <col width="15.1640625" customWidth="1" style="10" min="6" max="6"/>
+    <col width="34.1640625" customWidth="1" style="10" min="7" max="7"/>
+    <col width="54.83203125" customWidth="1" style="10" min="8" max="8"/>
+    <col width="29" customWidth="1" style="10" min="9" max="9"/>
+    <col width="17" bestFit="1" customWidth="1" style="10" min="10" max="10"/>
+    <col width="14.6640625" customWidth="1" style="10" min="11" max="11"/>
+    <col width="15.1640625" customWidth="1" style="10" min="12" max="12"/>
+    <col width="18.6640625" customWidth="1" style="10" min="13" max="13"/>
+    <col width="28.6640625" customWidth="1" style="10" min="14" max="14"/>
+    <col width="14.33203125" customWidth="1" style="10" min="15" max="15"/>
+    <col width="18.33203125" customWidth="1" style="10" min="16" max="16"/>
+    <col width="19.5" customWidth="1" style="10" min="17" max="17"/>
+    <col width="14.6640625" customWidth="1" style="10" min="18" max="18"/>
+    <col width="18.83203125" customWidth="1" style="10" min="19" max="19"/>
+    <col width="16.1640625" customWidth="1" style="10" min="20" max="20"/>
+    <col width="8.33203125" customWidth="1" style="10" min="21" max="22"/>
+    <col width="8.33203125" customWidth="1" style="10" min="23" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="R1" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="S1" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="T1" s="9" t="s">
-        <v>114</v>
+    <row r="1" ht="20.25" customHeight="1" s="17">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>ownerID</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>owner_codename</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>owner_fullname</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>personID</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>person_firstname</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>person_lastname</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>person_mbox</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>person_homepage</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>institutionID</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>institution_name</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>institution_mbox</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>institution_phone</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>institution_homepage</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>address_street</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>address_locality</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>address_postal_code</t>
+        </is>
+      </c>
+      <c r="Q1" s="9" t="inlineStr">
+        <is>
+          <t>address_country_code</t>
+        </is>
+      </c>
+      <c r="R1" s="9" t="inlineStr">
+        <is>
+          <t>address_country</t>
+        </is>
+      </c>
+      <c r="S1" s="9" t="inlineStr">
+        <is>
+          <t>affiliation_department</t>
+        </is>
+      </c>
+      <c r="T1" s="9" t="inlineStr">
+        <is>
+          <t>affiliation_function</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L2" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="N2" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="P2" s="15">
+    <row r="2" ht="20.25" customHeight="1" s="17">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/siteOwner/001</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>SITEOWNER</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>Site Owner Full Name</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/person/001</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Surname</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>someemail@domain.ab</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>https://www.domain.ab/person</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/institution/001</t>
+        </is>
+      </c>
+      <c r="J2" s="12" t="inlineStr">
+        <is>
+          <t>INSTITUTION_ABBR</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>info@domain.ab</t>
+        </is>
+      </c>
+      <c r="L2" s="14" t="inlineStr">
+        <is>
+          <t>+30 123 456789</t>
+        </is>
+      </c>
+      <c r="M2" s="12" t="inlineStr">
+        <is>
+          <t>http://www.domain.ab</t>
+        </is>
+      </c>
+      <c r="N2" s="12" t="inlineStr">
+        <is>
+          <t>Some streetAddress</t>
+        </is>
+      </c>
+      <c r="O2" s="12" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="P2" s="15" t="n">
         <v>12345</v>
       </c>
-      <c r="Q2" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="R2" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="S2" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="T2" s="12" t="s">
-        <v>133</v>
+      <c r="Q2" s="12" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="R2" s="12" t="inlineStr">
+        <is>
+          <t>Somecountry</t>
+        </is>
+      </c>
+      <c r="S2" s="12" t="inlineStr">
+        <is>
+          <t>Seismology</t>
+        </is>
+      </c>
+      <c r="T2" s="12" t="inlineStr">
+        <is>
+          <t>Senior researcher</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="isterre.fr/person/001" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="M2" r:id="rId2" display="http://www.isterre.fr" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" display="isterre.fr/person/001" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" display="http://www.isterre.fr" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
   <headerFooter>
+    <oddHeader/>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BH3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="9" width="16.33203125" customWidth="1"/>
-    <col min="10" max="10" width="19.6640625" customWidth="1"/>
-    <col min="11" max="62" width="16.33203125" customWidth="1"/>
+    <col width="16.33203125" customWidth="1" style="17" min="1" max="9"/>
+    <col width="19.6640625" customWidth="1" style="17" min="10" max="10"/>
+    <col width="16.33203125" customWidth="1" style="17" min="11" max="62"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" ht="32.25" customHeight="1" s="17">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>siteID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>siteDescriptionID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>station</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>altitude</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>minDistanceFromStation</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>maxDistanceFromStation</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8_qualityIndex</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8_title</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8_firstAuthor</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8_secondaryAuthors</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8_year</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8_booktitle</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8_language</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8_doi</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8_description</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>siteClassEC8_uri</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_value</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_uncertainty</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_qualityIndex</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_title</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_firstAuthor</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_secondaryAuthors</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_year</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_booktitle</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_language</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_doi</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_description</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>bedrockDepth_uri</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>h800_value</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>h800_uncertainty</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>h800_qualityIndex</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>h800_title</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>h800_firstAuthor</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>h800_secondaryAuthors</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>h800_year</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>h800_booktitle</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>h800_language</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>h800_doi</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>h800_description</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>h800_uri</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnit_value</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnit_qualityIndex</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalMapScale</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnitOGE</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnit_title</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnit_firstAuthor</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnit_secondaryAuthors</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnit_year</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnit_booktitle</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnit_language</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnit_doi</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnit_description</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>geologicalUnit_uri</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>morphology</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>topography_schemaA</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>topography_schemaB</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>overallQindex</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="128.25" customHeight="1" s="17">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site/001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site_description/001</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>XX.ABCD</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>45.137174</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>5.998905</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>239</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>Author A.</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="n"/>
+      <c r="N2" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Bulletin Earthquake Engineering</t>
+        </is>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>10.1007/s10518-017-0135-5</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="S2" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="U2" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="n"/>
+      <c r="X2" s="3" t="n"/>
+      <c r="Y2" s="3" t="n"/>
+      <c r="Z2" s="2" t="n"/>
+      <c r="AA2" s="3" t="n"/>
+      <c r="AB2" s="3" t="n"/>
+      <c r="AC2" s="3" t="n"/>
+      <c r="AD2" s="3" t="n"/>
+      <c r="AE2" s="3" t="n"/>
+      <c r="AF2" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="BF1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>59</v>
+      <c r="AG2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="6" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="AI2" s="3" t="inlineStr">
+        <is>
+          <t>Some title</t>
+        </is>
+      </c>
+      <c r="AJ2" s="6" t="inlineStr">
+        <is>
+          <t>Author A.</t>
+        </is>
+      </c>
+      <c r="AK2" s="3" t="n"/>
+      <c r="AL2" s="2" t="n"/>
+      <c r="AM2" s="3" t="n"/>
+      <c r="AN2" s="3" t="n"/>
+      <c r="AO2" s="3" t="n"/>
+      <c r="AP2" s="3" t="n"/>
+      <c r="AQ2" s="3" t="n"/>
+      <c r="AR2" s="2" t="inlineStr">
+        <is>
+          <t>Recent alluvial and lacustrine deposits valley overlying deep Jurassic limestones</t>
+        </is>
+      </c>
+      <c r="AS2" s="2" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="n"/>
+      <c r="AU2" s="3" t="n"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
+        </is>
+      </c>
+      <c r="AW2" s="6" t="inlineStr">
+        <is>
+          <t>Author A.</t>
+        </is>
+      </c>
+      <c r="AX2" s="3" t="n"/>
+      <c r="AY2" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AZ2" s="2" t="inlineStr">
+        <is>
+          <t>Bulletin Earthquake Engineering</t>
+        </is>
+      </c>
+      <c r="BA2" s="6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="BB2" s="2" t="inlineStr">
+        <is>
+          <t>10.1007/s10518-017-0135-5</t>
+        </is>
+      </c>
+      <c r="BC2" s="2" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="BD2" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
+        </is>
+      </c>
+      <c r="BE2" s="6" t="inlineStr">
+        <is>
+          <t>Valley - Basin</t>
+        </is>
+      </c>
+      <c r="BF2" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="BG2" s="2" t="inlineStr">
+        <is>
+          <t>Valley</t>
+        </is>
+      </c>
+      <c r="BH2" s="2" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:60" ht="128.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" s="3">
-        <v>239</v>
-      </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J2" s="3">
+    <row r="3" ht="44" customHeight="1" s="17">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site/002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site_description/002</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>YY.WXYZ</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>40.555907</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>22.988593</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="2">
-        <v>2018</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="T2" s="3">
-        <v>40</v>
-      </c>
-      <c r="U2" s="3">
-        <v>6</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3"/>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="3"/>
-      <c r="AE2" s="3"/>
-      <c r="AF2" s="3">
-        <v>10</v>
-      </c>
-      <c r="AG2" s="3">
-        <v>1</v>
-      </c>
-      <c r="AH2" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI2" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ2" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="AK2" s="3"/>
-      <c r="AL2" s="2"/>
-      <c r="AM2" s="3"/>
-      <c r="AN2" s="3"/>
-      <c r="AO2" s="3"/>
-      <c r="AP2" s="3"/>
-      <c r="AQ2" s="3"/>
-      <c r="AR2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AS2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AT2" s="3"/>
-      <c r="AU2" s="3"/>
-      <c r="AV2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AW2" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX2" s="3"/>
-      <c r="AY2" s="2">
-        <v>2018</v>
-      </c>
-      <c r="AZ2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="BA2" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="BB2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="BC2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="BD2" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="BE2" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="BF2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="BG2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="BH2" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:60" ht="44" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F3" s="5">
-        <v>120</v>
-      </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="M3" s="5"/>
-      <c r="N3" s="2">
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Combination of passive and active methods towards site characterization of accelerometer stations in Greece</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>Author B.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="O3" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q3" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="R3" s="5"/>
-      <c r="S3" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="T3" s="5">
+      <c r="O3" s="8" t="inlineStr">
+        <is>
+          <t>Near Surface Geophysics</t>
+        </is>
+      </c>
+      <c r="P3" s="8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="Q3" s="7" t="inlineStr">
+        <is>
+          <t>10.1002/nsg.12248</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="n"/>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/nsg.12248</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="n">
         <v>820</v>
       </c>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5">
+      <c r="U3" s="5" t="n"/>
+      <c r="V3" s="5" t="n">
         <v>0.8</v>
       </c>
-      <c r="W3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="X3" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="2">
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>Combination of passive and active methods towards site characterization of accelerometer stations in Greece</t>
+        </is>
+      </c>
+      <c r="X3" s="7" t="inlineStr">
+        <is>
+          <t>Author B.</t>
+        </is>
+      </c>
+      <c r="Y3" s="5" t="n"/>
+      <c r="Z3" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="AA3" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB3" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC3" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="AD3" s="5"/>
-      <c r="AE3" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="AF3" s="5">
+      <c r="AA3" s="8" t="inlineStr">
+        <is>
+          <t>Near Surface Geophysics</t>
+        </is>
+      </c>
+      <c r="AB3" s="8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AC3" s="7" t="inlineStr">
+        <is>
+          <t>10.1002/nsg.12248</t>
+        </is>
+      </c>
+      <c r="AD3" s="5" t="n"/>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/nsg.12248</t>
+        </is>
+      </c>
+      <c r="AF3" s="5" t="n">
         <v>180</v>
       </c>
-      <c r="AG3" s="5"/>
-      <c r="AH3" s="5"/>
-      <c r="AI3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AJ3" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AK3" s="5"/>
-      <c r="AL3" s="2">
+      <c r="AG3" s="5" t="n"/>
+      <c r="AH3" s="5" t="n"/>
+      <c r="AI3" s="2" t="inlineStr">
+        <is>
+          <t>Combination of passive and active methods towards site characterization of accelerometer stations in Greece</t>
+        </is>
+      </c>
+      <c r="AJ3" s="7" t="inlineStr">
+        <is>
+          <t>Author B.</t>
+        </is>
+      </c>
+      <c r="AK3" s="5" t="n"/>
+      <c r="AL3" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="AM3" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="AN3" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="AO3" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="AP3" s="5"/>
-      <c r="AQ3" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="AR3" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AS3" s="5"/>
-      <c r="AT3" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="AU3" s="5"/>
-      <c r="AV3" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="AW3" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="AX3" s="5"/>
-      <c r="AY3" s="2"/>
-      <c r="AZ3" s="5"/>
-      <c r="BA3" s="5"/>
-      <c r="BB3" s="5"/>
-      <c r="BC3" s="5"/>
-      <c r="BD3" s="5"/>
-      <c r="BE3" s="5"/>
-      <c r="BF3" s="5"/>
-      <c r="BG3" s="5"/>
-      <c r="BH3" s="5"/>
+      <c r="AM3" s="8" t="inlineStr">
+        <is>
+          <t>Near Surface Geophysics</t>
+        </is>
+      </c>
+      <c r="AN3" s="8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AO3" s="7" t="inlineStr">
+        <is>
+          <t>10.1002/nsg.12248</t>
+        </is>
+      </c>
+      <c r="AP3" s="5" t="n"/>
+      <c r="AQ3" s="4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/nsg.12248</t>
+        </is>
+      </c>
+      <c r="AR3" s="4" t="inlineStr">
+        <is>
+          <t>Holocene Deposits</t>
+        </is>
+      </c>
+      <c r="AS3" s="5" t="n"/>
+      <c r="AT3" s="4" t="inlineStr">
+        <is>
+          <t>01:50.0</t>
+        </is>
+      </c>
+      <c r="AU3" s="5" t="n"/>
+      <c r="AV3" s="4" t="inlineStr">
+        <is>
+          <t>IGME map</t>
+        </is>
+      </c>
+      <c r="AW3" s="4" t="inlineStr">
+        <is>
+          <t>IGME</t>
+        </is>
+      </c>
+      <c r="AX3" s="5" t="n"/>
+      <c r="AY3" s="2" t="n"/>
+      <c r="AZ3" s="5" t="n"/>
+      <c r="BA3" s="5" t="n"/>
+      <c r="BB3" s="5" t="n"/>
+      <c r="BC3" s="5" t="n"/>
+      <c r="BD3" s="5" t="n"/>
+      <c r="BE3" s="5" t="n"/>
+      <c r="BF3" s="5" t="n"/>
+      <c r="BG3" s="5" t="n"/>
+      <c r="BH3" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
   <headerFooter>
+    <oddHeader/>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>